--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-name.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>76</v>
